--- a/riobamba-censo-data/shp/plataforma_f.xlsx
+++ b/riobamba-censo-data/shp/plataforma_f.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -498,11 +498,12 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,25 +534,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>edad0_14</t>
+          <t>edad0_4</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>edad15_29</t>
+          <t>edad5_11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>edad30_44</t>
+          <t>edad12_17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>edad45_64</t>
+          <t>edad18_29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>edad30_64</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>edad65mas</t>
         </is>
@@ -581,15 +587,18 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>18</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -614,18 +623,21 @@
         <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>22</v>
       </c>
-      <c r="H3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I3" t="n">
-        <v>8</v>
-      </c>
       <c r="J3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -650,18 +662,21 @@
         <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>44</v>
+      </c>
+      <c r="J4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -686,18 +701,21 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
         <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -722,18 +740,21 @@
         <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -758,18 +779,21 @@
         <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -794,18 +818,21 @@
         <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" t="n">
         <v>10</v>
       </c>
     </row>
@@ -830,18 +857,21 @@
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J9" t="n">
+        <v>22</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,18 +896,21 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>16</v>
       </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
       <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,18 +935,21 @@
         <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -938,18 +974,21 @@
         <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -974,18 +1013,21 @@
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>14</v>
       </c>
-      <c r="H13" t="n">
-        <v>8</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
       <c r="J13" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1010,18 +1052,21 @@
         <v>31</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I14" t="n">
         <v>10</v>
       </c>
       <c r="J14" t="n">
+        <v>31</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1046,18 +1091,21 @@
         <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>35</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1082,18 +1130,21 @@
         <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
         <v>6</v>
       </c>
-      <c r="H16" t="n">
-        <v>17</v>
-      </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1118,18 +1169,21 @@
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1154,18 +1208,21 @@
         <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
+        <v>37</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1190,18 +1247,21 @@
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>20</v>
       </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>7</v>
-      </c>
       <c r="J19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1226,18 +1286,21 @@
         <v>23</v>
       </c>
       <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="n">
         <v>12</v>
       </c>
-      <c r="G20" t="n">
-        <v>15</v>
-      </c>
-      <c r="H20" t="n">
-        <v>14</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
       <c r="J20" t="n">
+        <v>19</v>
+      </c>
+      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1262,18 +1325,21 @@
         <v>44</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
+        <v>28</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1298,18 +1364,21 @@
         <v>69</v>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I22" t="n">
         <v>22</v>
       </c>
       <c r="J22" t="n">
+        <v>59</v>
+      </c>
+      <c r="K22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1334,18 +1403,21 @@
         <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
+        <v>44</v>
+      </c>
+      <c r="K23" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1370,18 +1442,21 @@
         <v>46</v>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>28</v>
+      </c>
+      <c r="J24" t="n">
         <v>33</v>
       </c>
-      <c r="H24" t="n">
-        <v>16</v>
-      </c>
-      <c r="I24" t="n">
-        <v>17</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1406,18 +1481,21 @@
         <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
+        <v>28</v>
+      </c>
+      <c r="K25" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1442,18 +1520,21 @@
         <v>41</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
+        <v>32</v>
+      </c>
+      <c r="K26" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1478,18 +1559,21 @@
         <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1514,18 +1598,21 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="H28" t="n">
-        <v>4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
       <c r="J28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1550,18 +1637,21 @@
         <v>28</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1586,18 +1676,21 @@
         <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
+        <v>42</v>
+      </c>
+      <c r="K30" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1622,18 +1715,21 @@
         <v>45</v>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
+        <v>37</v>
+      </c>
+      <c r="K31" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1658,18 +1754,21 @@
         <v>21</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
+        <v>19</v>
+      </c>
+      <c r="K32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1694,18 +1793,21 @@
         <v>51</v>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H33" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J33" t="n">
+        <v>40</v>
+      </c>
+      <c r="K33" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1730,18 +1832,21 @@
         <v>42</v>
       </c>
       <c r="F34" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J34" t="n">
+        <v>35</v>
+      </c>
+      <c r="K34" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1766,18 +1871,21 @@
         <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>25</v>
+      </c>
+      <c r="J35" t="n">
         <v>27</v>
       </c>
-      <c r="H35" t="n">
-        <v>21</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1805,15 +1913,18 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>25</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>5</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1838,18 +1949,21 @@
         <v>18</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
+        <v>17</v>
+      </c>
+      <c r="K37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1874,18 +1988,21 @@
         <v>7</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
+        <v>9</v>
+      </c>
+      <c r="K38" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1910,18 +2027,21 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
         <v>7</v>
       </c>
       <c r="J39" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1946,18 +2066,21 @@
         <v>57</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="J40" t="n">
+        <v>34</v>
+      </c>
+      <c r="K40" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1985,15 +2108,18 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2018,18 +2144,21 @@
         <v>73</v>
       </c>
       <c r="F42" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G42" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H42" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J42" t="n">
+        <v>54</v>
+      </c>
+      <c r="K42" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2054,18 +2183,21 @@
         <v>85</v>
       </c>
       <c r="F43" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J43" t="n">
+        <v>74</v>
+      </c>
+      <c r="K43" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2090,18 +2222,21 @@
         <v>31</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J44" t="n">
+        <v>25</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2126,18 +2261,21 @@
         <v>88</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H45" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
+        <v>72</v>
+      </c>
+      <c r="K45" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2162,18 +2300,21 @@
         <v>66</v>
       </c>
       <c r="F46" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
+        <v>54</v>
+      </c>
+      <c r="K46" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2198,18 +2339,21 @@
         <v>39</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="H47" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J47" t="n">
+        <v>21</v>
+      </c>
+      <c r="K47" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2237,15 +2381,18 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
+        <v>9</v>
+      </c>
+      <c r="K48" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2270,18 +2417,21 @@
         <v>63</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H49" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="J49" t="n">
+        <v>43</v>
+      </c>
+      <c r="K49" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2306,18 +2456,21 @@
         <v>23</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J50" t="n">
+        <v>13</v>
+      </c>
+      <c r="K50" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2342,18 +2495,21 @@
         <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
         <v>8</v>
       </c>
-      <c r="H51" t="n">
-        <v>4</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4</v>
-      </c>
       <c r="J51" t="n">
+        <v>8</v>
+      </c>
+      <c r="K51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2378,18 +2534,21 @@
         <v>21</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J52" t="n">
+        <v>14</v>
+      </c>
+      <c r="K52" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2414,18 +2573,21 @@
         <v>23</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
+        <v>19</v>
+      </c>
+      <c r="K53" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2450,18 +2612,21 @@
         <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>3</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2486,18 +2651,21 @@
         <v>46</v>
       </c>
       <c r="F55" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I55" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
+        <v>31</v>
+      </c>
+      <c r="K55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2522,18 +2690,21 @@
         <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
+        <v>28</v>
+      </c>
+      <c r="K56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2558,18 +2729,21 @@
         <v>29</v>
       </c>
       <c r="F57" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H57" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J57" t="n">
+        <v>22</v>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2594,18 +2768,21 @@
         <v>14</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J58" t="n">
+        <v>8</v>
+      </c>
+      <c r="K58" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2630,18 +2807,21 @@
         <v>11</v>
       </c>
       <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" t="n">
         <v>5</v>
       </c>
-      <c r="G59" t="n">
+      <c r="J59" t="n">
         <v>6</v>
       </c>
-      <c r="H59" t="n">
-        <v>3</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2666,18 +2846,21 @@
         <v>20</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>12</v>
+      </c>
+      <c r="J60" t="n">
         <v>13</v>
       </c>
-      <c r="H60" t="n">
-        <v>3</v>
-      </c>
-      <c r="I60" t="n">
-        <v>10</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2702,18 +2885,21 @@
         <v>61</v>
       </c>
       <c r="F61" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="H61" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J61" t="n">
+        <v>45</v>
+      </c>
+      <c r="K61" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2738,18 +2924,21 @@
         <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J62" t="n">
+        <v>35</v>
+      </c>
+      <c r="K62" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2774,18 +2963,21 @@
         <v>10</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
+        <v>14</v>
+      </c>
+      <c r="K63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2810,18 +3002,21 @@
         <v>115</v>
       </c>
       <c r="F64" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="G64" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H64" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J64" t="n">
+        <v>106</v>
+      </c>
+      <c r="K64" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2846,18 +3041,21 @@
         <v>5</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>1</v>
       </c>
-      <c r="H65" t="n">
-        <v>5</v>
-      </c>
-      <c r="I65" t="n">
-        <v>2</v>
-      </c>
       <c r="J65" t="n">
+        <v>7</v>
+      </c>
+      <c r="K65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2882,18 +3080,21 @@
         <v>74</v>
       </c>
       <c r="F66" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H66" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I66" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J66" t="n">
+        <v>66</v>
+      </c>
+      <c r="K66" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2918,18 +3119,21 @@
         <v>9</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
         <v>6</v>
       </c>
       <c r="J67" t="n">
+        <v>6</v>
+      </c>
+      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2954,18 +3158,21 @@
         <v>10</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2990,18 +3197,21 @@
         <v>26</v>
       </c>
       <c r="F69" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H69" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
+        <v>22</v>
+      </c>
+      <c r="K69" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3026,18 +3236,21 @@
         <v>21</v>
       </c>
       <c r="F70" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H70" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
+        <v>24</v>
+      </c>
+      <c r="K70" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3062,18 +3275,21 @@
         <v>27</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H71" t="n">
+        <v>8</v>
+      </c>
+      <c r="I71" t="n">
         <v>13</v>
       </c>
-      <c r="I71" t="n">
-        <v>16</v>
-      </c>
       <c r="J71" t="n">
+        <v>29</v>
+      </c>
+      <c r="K71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3098,18 +3314,21 @@
         <v>39</v>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
+        <v>42</v>
+      </c>
+      <c r="K72" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3134,18 +3353,21 @@
         <v>8</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
         <v>6</v>
       </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3170,18 +3392,21 @@
         <v>16</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J74" t="n">
+        <v>15</v>
+      </c>
+      <c r="K74" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3206,10 +3431,10 @@
         <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
         <v>3</v>
@@ -3218,6 +3443,9 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3242,18 +3470,21 @@
         <v>108</v>
       </c>
       <c r="F76" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="G76" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H76" t="n">
+        <v>32</v>
+      </c>
+      <c r="I76" t="n">
         <v>47</v>
       </c>
-      <c r="I76" t="n">
-        <v>39</v>
-      </c>
       <c r="J76" t="n">
+        <v>86</v>
+      </c>
+      <c r="K76" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3278,18 +3509,21 @@
         <v>26</v>
       </c>
       <c r="F77" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H77" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J77" t="n">
+        <v>17</v>
+      </c>
+      <c r="K77" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3314,18 +3548,21 @@
         <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
+        <v>9</v>
+      </c>
+      <c r="K78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3350,18 +3587,21 @@
         <v>20</v>
       </c>
       <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
         <v>8</v>
       </c>
-      <c r="G79" t="n">
-        <v>9</v>
-      </c>
-      <c r="H79" t="n">
-        <v>6</v>
-      </c>
-      <c r="I79" t="n">
-        <v>10</v>
-      </c>
       <c r="J79" t="n">
+        <v>16</v>
+      </c>
+      <c r="K79" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3386,18 +3626,21 @@
         <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H80" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J80" t="n">
+        <v>13</v>
+      </c>
+      <c r="K80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3422,18 +3665,21 @@
         <v>34</v>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>19</v>
+      </c>
+      <c r="J81" t="n">
         <v>24</v>
       </c>
-      <c r="H81" t="n">
-        <v>10</v>
-      </c>
-      <c r="I81" t="n">
-        <v>14</v>
-      </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3458,18 +3704,21 @@
         <v>48</v>
       </c>
       <c r="F82" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H82" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I82" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
+        <v>34</v>
+      </c>
+      <c r="K82" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3494,18 +3743,21 @@
         <v>45</v>
       </c>
       <c r="F83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J83" t="n">
+        <v>36</v>
+      </c>
+      <c r="K83" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3530,18 +3782,21 @@
         <v>17</v>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J84" t="n">
+        <v>14</v>
+      </c>
+      <c r="K84" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3566,18 +3821,21 @@
         <v>14</v>
       </c>
       <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4</v>
+      </c>
+      <c r="I85" t="n">
         <v>7</v>
       </c>
-      <c r="G85" t="n">
-        <v>9</v>
-      </c>
-      <c r="H85" t="n">
-        <v>5</v>
-      </c>
-      <c r="I85" t="n">
-        <v>6</v>
-      </c>
       <c r="J85" t="n">
+        <v>11</v>
+      </c>
+      <c r="K85" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3602,18 +3860,21 @@
         <v>15</v>
       </c>
       <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="n">
         <v>6</v>
       </c>
-      <c r="G86" t="n">
-        <v>18</v>
-      </c>
-      <c r="H86" t="n">
-        <v>9</v>
-      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
+        <v>14</v>
+      </c>
+      <c r="K86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3638,18 +3899,21 @@
         <v>51</v>
       </c>
       <c r="F87" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H87" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
+        <v>39</v>
+      </c>
+      <c r="K87" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3674,18 +3938,21 @@
         <v>22</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
+        <v>12</v>
+      </c>
+      <c r="K88" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3710,18 +3977,21 @@
         <v>29</v>
       </c>
       <c r="F89" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J89" t="n">
+        <v>21</v>
+      </c>
+      <c r="K89" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3746,18 +4016,21 @@
         <v>60</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H90" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I90" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J90" t="n">
+        <v>45</v>
+      </c>
+      <c r="K90" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3782,18 +4055,21 @@
         <v>5</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3818,18 +4094,21 @@
         <v>34</v>
       </c>
       <c r="F92" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H92" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J92" t="n">
+        <v>28</v>
+      </c>
+      <c r="K92" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3854,18 +4133,21 @@
         <v>33</v>
       </c>
       <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>10</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5</v>
+      </c>
+      <c r="I93" t="n">
         <v>16</v>
       </c>
-      <c r="G93" t="n">
-        <v>17</v>
-      </c>
-      <c r="H93" t="n">
-        <v>12</v>
-      </c>
-      <c r="I93" t="n">
-        <v>9</v>
-      </c>
       <c r="J93" t="n">
+        <v>21</v>
+      </c>
+      <c r="K93" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3890,18 +4172,21 @@
         <v>32</v>
       </c>
       <c r="F94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
         <v>7</v>
       </c>
-      <c r="G94" t="n">
-        <v>23</v>
-      </c>
-      <c r="H94" t="n">
-        <v>15</v>
-      </c>
       <c r="I94" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J94" t="n">
+        <v>28</v>
+      </c>
+      <c r="K94" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3926,18 +4211,21 @@
         <v>41</v>
       </c>
       <c r="F95" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G95" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H95" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J95" t="n">
+        <v>31</v>
+      </c>
+      <c r="K95" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3962,18 +4250,21 @@
         <v>43</v>
       </c>
       <c r="F96" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G96" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H96" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J96" t="n">
+        <v>35</v>
+      </c>
+      <c r="K96" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3998,18 +4289,21 @@
         <v>41</v>
       </c>
       <c r="F97" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H97" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I97" t="n">
         <v>11</v>
       </c>
       <c r="J97" t="n">
+        <v>32</v>
+      </c>
+      <c r="K97" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4034,18 +4328,21 @@
         <v>9</v>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
+        <v>8</v>
+      </c>
+      <c r="K98" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4070,18 +4367,21 @@
         <v>55</v>
       </c>
       <c r="F99" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G99" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H99" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I99" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J99" t="n">
+        <v>49</v>
+      </c>
+      <c r="K99" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4106,18 +4406,21 @@
         <v>35</v>
       </c>
       <c r="F100" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G100" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H100" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I100" t="n">
         <v>17</v>
       </c>
       <c r="J100" t="n">
+        <v>30</v>
+      </c>
+      <c r="K100" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4142,18 +4445,21 @@
         <v>62</v>
       </c>
       <c r="F101" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H101" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I101" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J101" t="n">
+        <v>41</v>
+      </c>
+      <c r="K101" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4178,18 +4484,21 @@
         <v>31</v>
       </c>
       <c r="F102" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H102" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I102" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J102" t="n">
+        <v>24</v>
+      </c>
+      <c r="K102" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4214,18 +4523,21 @@
         <v>55</v>
       </c>
       <c r="F103" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G103" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H103" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I103" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J103" t="n">
+        <v>42</v>
+      </c>
+      <c r="K103" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4250,18 +4562,21 @@
         <v>40</v>
       </c>
       <c r="F104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I104" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="J104" t="n">
+        <v>23</v>
+      </c>
+      <c r="K104" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4286,18 +4601,21 @@
         <v>44</v>
       </c>
       <c r="F105" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H105" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J105" t="n">
+        <v>39</v>
+      </c>
+      <c r="K105" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4322,18 +4640,21 @@
         <v>35</v>
       </c>
       <c r="F106" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G106" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H106" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I106" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J106" t="n">
+        <v>18</v>
+      </c>
+      <c r="K106" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4358,18 +4679,21 @@
         <v>36</v>
       </c>
       <c r="F107" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H107" t="n">
+        <v>6</v>
+      </c>
+      <c r="I107" t="n">
         <v>15</v>
       </c>
-      <c r="I107" t="n">
-        <v>13</v>
-      </c>
       <c r="J107" t="n">
+        <v>28</v>
+      </c>
+      <c r="K107" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4394,18 +4718,21 @@
         <v>48</v>
       </c>
       <c r="F108" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H108" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I108" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J108" t="n">
+        <v>36</v>
+      </c>
+      <c r="K108" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4430,18 +4757,21 @@
         <v>35</v>
       </c>
       <c r="F109" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H109" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I109" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J109" t="n">
+        <v>35</v>
+      </c>
+      <c r="K109" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4466,18 +4796,21 @@
         <v>28</v>
       </c>
       <c r="F110" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H110" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I110" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J110" t="n">
+        <v>26</v>
+      </c>
+      <c r="K110" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4502,18 +4835,21 @@
         <v>30</v>
       </c>
       <c r="F111" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G111" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H111" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J111" t="n">
+        <v>28</v>
+      </c>
+      <c r="K111" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4538,18 +4874,21 @@
         <v>117</v>
       </c>
       <c r="F112" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" t="n">
+        <v>22</v>
+      </c>
+      <c r="H112" t="n">
+        <v>17</v>
+      </c>
+      <c r="I112" t="n">
         <v>39</v>
       </c>
-      <c r="G112" t="n">
-        <v>49</v>
-      </c>
-      <c r="H112" t="n">
-        <v>64</v>
-      </c>
-      <c r="I112" t="n">
-        <v>44</v>
-      </c>
       <c r="J112" t="n">
+        <v>108</v>
+      </c>
+      <c r="K112" t="n">
         <v>21</v>
       </c>
     </row>
@@ -4574,18 +4913,21 @@
         <v>20</v>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
+        <v>5</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" t="n">
         <v>6</v>
       </c>
-      <c r="H113" t="n">
-        <v>6</v>
-      </c>
-      <c r="I113" t="n">
-        <v>8</v>
-      </c>
       <c r="J113" t="n">
+        <v>14</v>
+      </c>
+      <c r="K113" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4610,18 +4952,21 @@
         <v>42</v>
       </c>
       <c r="F114" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H114" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I114" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J114" t="n">
+        <v>36</v>
+      </c>
+      <c r="K114" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4646,18 +4991,21 @@
         <v>57</v>
       </c>
       <c r="F115" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="H115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="J115" t="n">
+        <v>22</v>
+      </c>
+      <c r="K115" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4685,15 +5033,18 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4718,18 +5069,21 @@
         <v>48</v>
       </c>
       <c r="F117" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
+        <v>4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>7</v>
+      </c>
+      <c r="I117" t="n">
+        <v>34</v>
+      </c>
+      <c r="J117" t="n">
         <v>36</v>
       </c>
-      <c r="H117" t="n">
-        <v>16</v>
-      </c>
-      <c r="I117" t="n">
-        <v>20</v>
-      </c>
-      <c r="J117" t="n">
+      <c r="K117" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4754,18 +5108,21 @@
         <v>42</v>
       </c>
       <c r="F118" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G118" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I118" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J118" t="n">
+        <v>30</v>
+      </c>
+      <c r="K118" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4790,18 +5147,21 @@
         <v>55</v>
       </c>
       <c r="F119" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H119" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I119" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J119" t="n">
+        <v>31</v>
+      </c>
+      <c r="K119" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4826,18 +5186,21 @@
         <v>26</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I120" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J120" t="n">
+        <v>16</v>
+      </c>
+      <c r="K120" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4862,18 +5225,21 @@
         <v>27</v>
       </c>
       <c r="F121" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+      <c r="I121" t="n">
+        <v>20</v>
+      </c>
+      <c r="J121" t="n">
         <v>21</v>
       </c>
-      <c r="H121" t="n">
-        <v>10</v>
-      </c>
-      <c r="I121" t="n">
-        <v>11</v>
-      </c>
-      <c r="J121" t="n">
+      <c r="K121" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4898,18 +5264,21 @@
         <v>53</v>
       </c>
       <c r="F122" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I122" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="J122" t="n">
+        <v>23</v>
+      </c>
+      <c r="K122" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4934,18 +5303,21 @@
         <v>25</v>
       </c>
       <c r="F123" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" t="n">
+        <v>11</v>
+      </c>
+      <c r="I123" t="n">
+        <v>8</v>
+      </c>
+      <c r="J123" t="n">
         <v>18</v>
       </c>
-      <c r="G123" t="n">
-        <v>14</v>
-      </c>
-      <c r="H123" t="n">
-        <v>5</v>
-      </c>
-      <c r="I123" t="n">
-        <v>13</v>
-      </c>
-      <c r="J123" t="n">
+      <c r="K123" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4970,18 +5342,21 @@
         <v>48</v>
       </c>
       <c r="F124" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H124" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I124" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J124" t="n">
+        <v>38</v>
+      </c>
+      <c r="K124" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5006,18 +5381,21 @@
         <v>32</v>
       </c>
       <c r="F125" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G125" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H125" t="n">
         <v>11</v>
       </c>
       <c r="I125" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J125" t="n">
+        <v>24</v>
+      </c>
+      <c r="K125" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5042,18 +5420,21 @@
         <v>5</v>
       </c>
       <c r="F126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
         <v>5</v>
       </c>
-      <c r="H126" t="n">
-        <v>3</v>
-      </c>
-      <c r="I126" t="n">
-        <v>3</v>
-      </c>
       <c r="J126" t="n">
+        <v>6</v>
+      </c>
+      <c r="K126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5078,18 +5459,21 @@
         <v>36</v>
       </c>
       <c r="F127" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G127" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H127" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I127" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J127" t="n">
+        <v>26</v>
+      </c>
+      <c r="K127" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5114,18 +5498,21 @@
         <v>25</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
         <v>32</v>
       </c>
-      <c r="H128" t="n">
-        <v>7</v>
-      </c>
-      <c r="I128" t="n">
-        <v>9</v>
-      </c>
       <c r="J128" t="n">
+        <v>16</v>
+      </c>
+      <c r="K128" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5150,23 +5537,26 @@
         <v>49</v>
       </c>
       <c r="F129" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G129" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H129" t="n">
+        <v>15</v>
+      </c>
+      <c r="I129" t="n">
         <v>17</v>
       </c>
-      <c r="I129" t="n">
-        <v>22</v>
-      </c>
       <c r="J129" t="n">
+        <v>39</v>
+      </c>
+      <c r="K129" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>